--- a/data.mn/public/datasets/mongolbank-usd-mnt-monthly.xlsx
+++ b/data.mn/public/datasets/mongolbank-usd-mnt-monthly.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B405"/>
+  <dimension ref="A1:B406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4471,6 +4471,16 @@
       </c>
       <c r="B405" t="n">
         <v>3594.47</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>3595.44</v>
       </c>
     </row>
   </sheetData>
@@ -4484,7 +4494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B405"/>
+  <dimension ref="A1:B406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8543,6 +8553,16 @@
         <v>3594.47</v>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>3595.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
